--- a/data/canary/valcan_pack_2026-04-12/_VALCAN_2026/20_LOGISTICS/valcanary_oconus_shipment_crosswalk.xlsx
+++ b/data/canary/valcan_pack_2026-04-12/_VALCAN_2026/20_LOGISTICS/valcanary_oconus_shipment_crosswalk.xlsx
@@ -589,17 +589,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VALSITE-BRAVO</t>
+          <t>Site: Validation Bravo Site</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VALPO-9000000002</t>
+          <t>PO 9001000002</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VALPART-UPS48V-003</t>
+          <t>QZ-3003</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -621,17 +621,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VALSITE-CHARLIE</t>
+          <t>Site: Validation Charlie Site</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VALPO-9000000004</t>
+          <t>PO 9001000004</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VALPART-GPSANT-004</t>
+          <t>QZ-3004</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -653,17 +653,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VALSITE-ECHO</t>
+          <t>Site: Validation Echo Site</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>VALPO-9000000006</t>
+          <t>PO 9001000006</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VALPART-ROUTER-016</t>
+          <t>QZ-3016</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
